--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_47_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_47_IN_Piura.xlsx
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>41.25</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="C11" s="31">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>48.91</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>9.84</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1915,11 +1915,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>13.5513</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>12.2177</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>90.16</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1965,11 +1965,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>1.3336</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>9.84</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2125,11 +2125,11 @@
       </c>
       <c r="B27" s="22">
         <f>SUM(B25:B26)</f>
-        <v/>
+        <v>13.5536</v>
       </c>
       <c r="C27" s="23">
         <f>SUM(C25:C26)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
       <c r="E27" s="17" t="inlineStr"/>
@@ -2248,6 +2248,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2365,6 +2366,7 @@
       <c r="F12" s="17" t="inlineStr"/>
       <c r="G12" s="17" t="inlineStr"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
@@ -2413,6 +2415,7 @@
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="120" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
@@ -2797,11 +2800,11 @@
       </c>
       <c r="B17" s="33">
         <f>SUM(B10:B16)</f>
-        <v/>
+        <v>273.96</v>
       </c>
       <c r="C17" s="23">
         <f>SUM(C10:C16)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -2811,19 +2814,19 @@
       <c r="E17" s="17" t="inlineStr"/>
       <c r="F17" s="17">
         <f>ROUND(AVERAGE(F10:F16),2)</f>
-        <v/>
+        <v>29.26</v>
       </c>
       <c r="G17" s="22">
         <f>ROUND(AVERAGE(G10:G16),4)</f>
-        <v/>
+        <v>0.5792</v>
       </c>
       <c r="H17" s="23">
         <f>ROUND(AVERAGE(H10:H16),2)</f>
-        <v/>
+        <v>90.14</v>
       </c>
       <c r="I17" s="23">
         <f>ROUND(AVERAGE(I10:I16),2)</f>
-        <v/>
+        <v>14.61</v>
       </c>
     </row>
     <row r="18"/>
